--- a/data/trans_orig/P21D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43682</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36898</t>
+          <t>41522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>39703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72563</t>
+          <t>70575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>111473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133028</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88980</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110138</t>
+          <t>109948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207599</t>
+          <t>209756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238934</t>
+          <t>240167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72385</t>
+          <t>73387</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43048</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65519</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106073</t>
+          <t>110970</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131688</t>
+          <t>131880</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167254</t>
+          <t>167943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186775</t>
+          <t>185541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208035</t>
+          <t>208260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329344</t>
+          <t>324192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370236</t>
+          <t>368887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115187</t>
+          <t>116624</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131164</t>
+          <t>131594</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191544</t>
+          <t>191353</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>211667</t>
+          <t>212368</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58452</t>
+          <t>59501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59342</t>
+          <t>61661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186171</t>
+          <t>180553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102815</t>
+          <t>104140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>266456</t>
+          <t>252137</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72594</t>
+          <t>72650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102616</t>
+          <t>101464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177045</t>
+          <t>175757</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>128051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265448</t>
+          <t>263852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24142</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>43896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49136</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61135</t>
+          <t>61888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91019</t>
+          <t>90836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110632</t>
+          <t>110120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113377</t>
+          <t>113454</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122566</t>
+          <t>122407</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102207</t>
+          <t>103074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109402</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219651</t>
+          <t>219958</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230482</t>
+          <t>230638</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>56609</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>93972</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>60698</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>96771</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>144674</t>
+          <t>145510</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>210546</t>
+          <t>210932</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>248558</t>
+          <t>249580</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>237813</t>
+          <t>239311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>264196</t>
+          <t>265532</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>458426</t>
+          <t>458521</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>506737</t>
+          <t>508856</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>207057</t>
+          <t>206447</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>79650</t>
+          <t>78268</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>108916</t>
+          <t>109131</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>87386</t>
+          <t>99024</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>287525</t>
+          <t>288354</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>346620</t>
+          <t>347229</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>515426</t>
+          <t>519321</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>234782</t>
+          <t>235694</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>264472</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>608290</t>
+          <t>607684</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>814000</t>
+          <t>802675</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4959,77 +4959,77 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>10324</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>10822</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>10055</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>5075</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>10397</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>219253</t>
+          <t>215490</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>433588</t>
+          <t>430323</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>276550</t>
+          <t>277201</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>535091</t>
+          <t>535322</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>566544</t>
+          <t>569493</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>871893</t>
+          <t>879865</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1199514</t>
+          <t>1200333</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1435166</t>
+          <t>1422602</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1027660</t>
+          <t>1032877</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1283586</t>
+          <t>1283367</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2331560</t>
+          <t>2317847</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2642692</t>
+          <t>2635653</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>79425</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>47027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41522</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54165</t>
+          <t>56520</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70575</t>
+          <t>70682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123305</t>
+          <t>119481</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111473</t>
+          <t>107260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134131</t>
+          <t>128538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>102567</t>
+          <t>116497</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>107008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109948</t>
+          <t>123279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>225872</t>
+          <t>235978</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209756</t>
+          <t>222582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240167</t>
+          <t>249494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>498</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53837</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73387</t>
+          <t>74865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>86175</t>
+          <t>91115</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67018</t>
+          <t>71215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110970</t>
+          <t>115747</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>151222</t>
+          <t>160321</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131880</t>
+          <t>140835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167943</t>
+          <t>176365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>198384</t>
+          <t>209663</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185541</t>
+          <t>195682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208260</t>
+          <t>220786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>349607</t>
+          <t>369984</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324192</t>
+          <t>345951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>368887</t>
+          <t>391479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31562</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>40770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>68559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124682</t>
+          <t>126050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116624</t>
+          <t>117785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131594</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>202949</t>
+          <t>202871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191353</t>
+          <t>191933</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212368</t>
+          <t>211264</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>64920</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>83389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116344</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>43794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180553</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>160441</t>
+          <t>119766</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104140</t>
+          <t>99430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252137</t>
+          <t>141978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>88019</t>
+          <t>99092</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72650</t>
+          <t>80309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101464</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>123349</t>
+          <t>139327</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63071</t>
+          <t>124818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175757</t>
+          <t>151524</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>211368</t>
+          <t>238419</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128051</t>
+          <t>212835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263852</t>
+          <t>258994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16620</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33733</t>
+          <t>44005</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>34218</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>54881</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>50868</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37236</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>58680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56287</t>
+          <t>61650</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50237</t>
+          <t>54306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61888</t>
+          <t>67094</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>101696</t>
+          <t>112518</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>102328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110120</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119129</t>
+          <t>118956</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113454</t>
+          <t>112425</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122407</t>
+          <t>123191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>107018</t>
+          <t>109789</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103074</t>
+          <t>105088</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109684</t>
+          <t>112131</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>226148</t>
+          <t>228745</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219958</t>
+          <t>221763</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230638</t>
+          <t>233638</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>72478</t>
+          <t>78553</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55920</t>
+          <t>60033</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>94527</t>
+          <t>99602</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>60698</t>
+          <t>67987</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>119475</t>
+          <t>131268</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>96771</t>
+          <t>110239</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>145510</t>
+          <t>158451</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>231987</t>
+          <t>266111</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>210932</t>
+          <t>243007</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>249580</t>
+          <t>285104</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>253240</t>
+          <t>296592</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>239311</t>
+          <t>279688</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>265532</t>
+          <t>308894</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>485227</t>
+          <t>562703</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>458521</t>
+          <t>534496</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>508856</t>
+          <t>585037</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>133132</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>114932</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>206447</t>
+          <t>153863</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>93116</t>
+          <t>114101</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>98948</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>134314</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>203318</t>
+          <t>247233</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>99024</t>
+          <t>219717</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>288354</t>
+          <t>276035</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>443553</t>
+          <t>226375</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>347229</t>
+          <t>206025</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>519321</t>
+          <t>244420</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>251077</t>
+          <t>288859</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>235694</t>
+          <t>268392</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>265260</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>694629</t>
+          <t>515234</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>607684</t>
+          <t>485244</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>802675</t>
+          <t>540556</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>355145</t>
+          <t>419429</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>215490</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>430323</t>
+          <t>462742</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>344124</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>287162</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>535322</t>
+          <t>344682</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>699268</t>
+          <t>732394</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>569493</t>
+          <t>680259</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>879865</t>
+          <t>785874</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1280892</t>
+          <t>1118025</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1200333</t>
+          <t>1073216</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1422602</t>
+          <t>1157753</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1216604</t>
+          <t>1348428</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1032877</t>
+          <t>1316039</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1283367</t>
+          <t>1377198</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2497496</t>
+          <t>2466454</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2317847</t>
+          <t>2414253</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2635653</t>
+          <t>2517654</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>45318</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>50519</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>86728</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
